--- a/out/Attention-mamba2_repeat_1_000007.xlsx
+++ b/out/Attention-mamba2_repeat_1_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.481593977180773</v>
+        <v>6.558570929792915</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.481593977180773</v>
+        <v>6.558570929792915</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.358776160273009</v>
+        <v>7.158570929792915</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.481593977180773</v>
+        <v>7.158570929792915</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.481593977180773</v>
+        <v>7.158570929792915</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.481593977180773</v>
+        <v>0.01422621125862855</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.481593977180773</v>
+        <v>0.01422621125862855</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-5.532999520923477e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>0.6378731275981827</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC40" t="n">
-        <v>-6.208018686342984e-05</v>
+        <v>1.276732291935469</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>-0.08005177821598476</v>
+        <v>0.09565192089224188</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC41" t="n">
-        <v>-0.08011385840284813</v>
+        <v>0.8293068926450892</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.1195960242376086</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC42" t="n">
-        <v>-0.08017026020806597</v>
+        <v>0.9728622104201675</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.09415875728379076</v>
+        <v>0.1714401708973075</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.1083736465650096</v>
+        <v>1.196214346911148</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1295423185513506</v>
+        <v>0.1834073720878032</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2733106879317074</v>
+        <v>1.391601377134836</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1514413920376537</v>
+        <v>0.1943741091984331</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4466636495303477</v>
+        <v>1.596957578489285</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.06772744862596136</v>
+        <v>0.08771808622367523</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4305394400139253</v>
+        <v>1.577856640906283</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03260093878039496</v>
+        <v>0.04236382635570257</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4279569788866034</v>
+        <v>1.574797424428305</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.015459574446222</v>
+        <v>0.02018510200709457</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4262456160362786</v>
+        <v>1.572770159335412</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004254914822619475</v>
+        <v>0.005977170995344169</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4192817897837297</v>
+        <v>1.564521796049247</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002940328655381489</v>
+        <v>0.00395245841703629</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.420905658416498</v>
+        <v>1.566446316909934</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00150755291679029</v>
+        <v>0.002019979631681313</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4209776008381557</v>
+        <v>1.566532448679777</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0007710088587970488</v>
+        <v>0.001030855339446593</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4210110483416554</v>
+        <v>1.566572997859534</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002741546204824301</v>
+        <v>0.0003847957323492379</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4207883296535034</v>
+        <v>1.566309941789069</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001493595802776238</v>
+        <v>0.0002070265361554608</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4208127794049613</v>
+        <v>1.566339807494177</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>6.923537046414474e-05</v>
+        <v>9.752016362202436e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4208010655070001</v>
+        <v>1.566326861688333</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.199531502110222e-05</v>
+        <v>5.797312751584259e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4208166511421427</v>
+        <v>1.566346224394334</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.972383659191222e-05</v>
+        <v>2.793981303953445e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4208141180978729</v>
+        <v>1.566344139773606</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.395902747928427e-06</v>
+        <v>1.098549009256284e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4208082523249287</v>
+        <v>1.566338120006411</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.158324102806951e-06</v>
+        <v>5.233171022101693e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4208071669128099</v>
+        <v>1.566337874210848</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.844180684889389e-06</v>
+        <v>-3.375548894532629e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4208013669637186</v>
+        <v>1.566331845502561</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.168604696895391e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4207958188354976</v>
+        <v>1.566326160968533</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.001043275021943e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4207909842011791</v>
+        <v>1.566321409693319</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4207908402172716</v>
+        <v>1.566316120545757</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4207908174829702</v>
+        <v>1.566316097811456</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4207911357631869</v>
+        <v>1.566316416091672</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4207922270096438</v>
+        <v>1.566317507338129</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4207915374025079</v>
+        <v>1.566316817730993</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4207915677149096</v>
+        <v>1.566316848043395</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4207913782623995</v>
+        <v>1.566316658590885</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4207914313091023</v>
+        <v>1.566316711637588</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4207914843558052</v>
+        <v>1.566316764684291</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4207914464653032</v>
+        <v>1.566316726793788</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4207913176375965</v>
+        <v>1.566316597966082</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.420791173653689</v>
+        <v>1.566316453982174</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4207910145135806</v>
+        <v>1.566316294842066</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4207910675602834</v>
+        <v>1.566316347888769</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4207910145135806</v>
+        <v>1.566316294842066</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4207910145135806</v>
+        <v>1.566316294842066</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4207908326391711</v>
+        <v>1.566316112967656</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4207909993573797</v>
+        <v>1.566316279685865</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4207911963879901</v>
+        <v>1.566316476716476</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4207910372478817</v>
+        <v>1.566316317576367</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4207910751383838</v>
+        <v>1.566316355466869</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4207912721689939</v>
+        <v>1.56631655249748</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4207912494346928</v>
+        <v>1.566316529763178</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4207910978726849</v>
+        <v>1.56631637820117</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4207910220916809</v>
+        <v>1.566316302420166</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4207911206069861</v>
+        <v>1.566316400935472</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4207911281850864</v>
+        <v>1.566316408513572</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4207913934186003</v>
+        <v>1.566316673747086</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4207910978726849</v>
+        <v>1.56631637820117</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4207913403718977</v>
+        <v>1.566316620700383</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.420791423731002</v>
+        <v>1.566316704059487</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4207912570127934</v>
+        <v>1.566316537341278</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4207914464653032</v>
+        <v>1.566316726793788</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4207910978726849</v>
+        <v>1.56631637820117</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4207908932639742</v>
+        <v>1.56631617359246</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4207910069354803</v>
+        <v>1.566316287263966</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4207910220916809</v>
+        <v>1.566316302420166</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4207907871705687</v>
+        <v>1.566316067499054</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4207908477953719</v>
+        <v>1.566316128123857</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4207907189676652</v>
+        <v>1.566315999296151</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4207908553734722</v>
+        <v>1.566316135701958</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4207910296697814</v>
+        <v>1.566316309998267</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.420791173653689</v>
+        <v>1.566316453982174</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4207910069354803</v>
+        <v>1.566316287263966</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4207909993573797</v>
+        <v>1.566316279685865</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4207907113895647</v>
+        <v>1.56631599171805</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4207907265457655</v>
+        <v>1.566316006874251</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4207909538887774</v>
+        <v>1.566316234217263</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4207909387325766</v>
+        <v>1.566316219061062</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4207910448259821</v>
+        <v>1.566316325154467</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4207907720143679</v>
+        <v>1.566316052342853</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4207908705296731</v>
+        <v>1.566316150858159</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4207910220916809</v>
+        <v>1.566316302420166</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4207910372478817</v>
+        <v>1.566316317576367</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4207910145135806</v>
+        <v>1.566316294842066</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4207910978726849</v>
+        <v>1.56631637820117</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4207911963879901</v>
+        <v>1.566316476716476</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4207910296697814</v>
+        <v>1.566316309998267</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4207910145135806</v>
+        <v>1.566316294842066</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4207909842011791</v>
+        <v>1.566316264529664</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4207909690449783</v>
+        <v>1.566316249373463</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4207910069354803</v>
+        <v>1.566316287263966</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4207910220916809</v>
+        <v>1.566316302420166</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.970767248321669e-06</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5857737887413714</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4207910145135806</v>
+        <v>1.566316294842066</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_1_000007.xlsx
+++ b/out/Attention-mamba2_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-3.516261771006975e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>0.4053729746823554</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC40" t="n">
-        <v>-6.208018686342984e-05</v>
+        <v>0.8113727343818626</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>-0.08005177821598476</v>
+        <v>0.06078750852185627</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC41" t="n">
-        <v>-0.08011385840284813</v>
+        <v>0.5270305589340839</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.07600410788781901</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC42" t="n">
-        <v>-0.08017026020806597</v>
+        <v>0.6182610332445521</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.09415875728379076</v>
+        <v>0.1089515282151813</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.1083736465650096</v>
+        <v>0.760203086455992</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1295423185513506</v>
+        <v>0.116556902154839</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2733106879317074</v>
+        <v>0.8843731604550048</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1514413920376537</v>
+        <v>0.1235268231524168</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4466636495303477</v>
+        <v>1.014878724464581</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.06772744862596136</v>
+        <v>0.05574469197845421</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4305394400139253</v>
+        <v>1.002739967705321</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03260093878039496</v>
+        <v>0.02692278149100792</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4279569788866034</v>
+        <v>1.000795794483602</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.015459574446222</v>
+        <v>0.01282679925930463</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4262456160362786</v>
+        <v>0.9995063356691005</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004254914822619475</v>
+        <v>0.00379661771500555</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120558</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4192817897837297</v>
+        <v>0.9942625675800382</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002940328655381489</v>
+        <v>0.002509625022824128</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120558</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.420905658416498</v>
+        <v>0.9954838473327164</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00150755291679029</v>
+        <v>0.001282013293605033</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4209776008381557</v>
+        <v>0.9955367761012688</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0007710088587970488</v>
+        <v>0.0006533570378990008</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.6502358700668159</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4210110483416554</v>
+        <v>0.9955607340108159</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002741546204824301</v>
+        <v>0.0002425013679188365</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4207883296535034</v>
+        <v>0.9953916308557508</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001493595802776238</v>
+        <v>0.0001303009802704108</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4208127794049613</v>
+        <v>0.9954088362657181</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>6.923537046414474e-05</v>
+        <v>6.016785594578292e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4208010655070001</v>
+        <v>0.9953987854433987</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.199531502110222e-05</v>
+        <v>3.534215981483665e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4208166511421427</v>
+        <v>0.9954092714339162</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.972383659191222e-05</v>
+        <v>1.558738314970903e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120558</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4208141180978729</v>
+        <v>0.9954061105966873</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.395902747928427e-06</v>
+        <v>4.990931307851776e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4208082523249287</v>
+        <v>0.9954004618750396</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.158324102806951e-06</v>
+        <v>1.395731888813558e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120559</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4208071669128099</v>
+        <v>0.9953985383989552</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.844180684889389e-06</v>
+        <v>-1.503166167089948e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4208013669637186</v>
+        <v>0.99539285212137</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.168604696895391e-06</v>
+        <v>-3.970630842514548e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.6502358700668159</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4207958188354976</v>
+        <v>0.9953874416514523</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.001043275021943e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4207909842011791</v>
+        <v>0.9953826070171339</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4207908402172716</v>
+        <v>0.9953824630332263</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120557</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4207908174829702</v>
+        <v>0.995382440298925</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4207911357631869</v>
+        <v>0.9953827585791417</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4207922270096438</v>
+        <v>0.9953838498255986</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4207915374025079</v>
+        <v>0.9953831602184626</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4207915677149096</v>
+        <v>0.9953831905308643</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120558</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4207913782623995</v>
+        <v>0.9953830010783542</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4207914313091023</v>
+        <v>0.9953830541250571</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4207914843558052</v>
+        <v>0.9953831071717599</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4207914464653032</v>
+        <v>0.995383069281258</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4207913176375965</v>
+        <v>0.9953829404535512</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.420791173653689</v>
+        <v>0.9953827964696437</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4207910145135806</v>
+        <v>0.9953826373295354</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120557</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4207910675602834</v>
+        <v>0.9953826903762382</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4207910145135806</v>
+        <v>0.9953826373295354</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120559</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4207910145135806</v>
+        <v>0.9953826373295354</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4207908326391711</v>
+        <v>0.9953824554551258</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4207909993573797</v>
+        <v>0.9953826221733345</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4207911963879901</v>
+        <v>0.9953828192039449</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4207910372478817</v>
+        <v>0.9953826600638365</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4207910751383838</v>
+        <v>0.9953826979543385</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.850235870066816</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4207912721689939</v>
+        <v>0.9953828949849487</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4207912494346928</v>
+        <v>0.9953828722506475</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120557</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4207910978726849</v>
+        <v>0.9953827206886396</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4207910220916809</v>
+        <v>0.9953826449076356</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120559</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4207911206069861</v>
+        <v>0.9953827434229409</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.881593977180773</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4207911281850864</v>
+        <v>0.9953827510010411</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4207913934186003</v>
+        <v>0.9953830162345551</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4207910978726849</v>
+        <v>0.9953827206886396</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4207913403718977</v>
+        <v>0.9953829631878524</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.481593977180773</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.420791423731002</v>
+        <v>0.9953830465469568</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120557</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4207912570127934</v>
+        <v>0.9953828798287481</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120558</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4207914464653032</v>
+        <v>0.995383069281258</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.881593977180773</v>
+        <v>0.6482190499120558</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4207910978726849</v>
+        <v>0.9953827206886396</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120558</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4207908932639742</v>
+        <v>0.995382516079929</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4207910069354803</v>
+        <v>0.995382629751435</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4207910220916809</v>
+        <v>0.9953826449076356</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4207907871705687</v>
+        <v>0.9953824099865235</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4207908477953719</v>
+        <v>0.9953824706113267</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120558</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4207907189676652</v>
+        <v>0.99538234178362</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.481593977180773</v>
+        <v>0.4482190499120557</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4207908553734722</v>
+        <v>0.9953824781894269</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120557</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4207910296697814</v>
+        <v>0.9953826524857362</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.420791173653689</v>
+        <v>0.9953827964696437</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4207910069354803</v>
+        <v>0.995382629751435</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4207909993573797</v>
+        <v>0.9953826221733345</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4207907113895647</v>
+        <v>0.9953823342055194</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4207907265457655</v>
+        <v>0.9953823493617202</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4207909538887774</v>
+        <v>0.9953825767047322</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4207909387325766</v>
+        <v>0.9953825615485313</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4207910448259821</v>
+        <v>0.9953826676419368</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.358776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4207907720143679</v>
+        <v>0.9953823948303225</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4207908705296731</v>
+        <v>0.9953824933456278</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4207910220916809</v>
+        <v>0.9953826449076356</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4207910372478817</v>
+        <v>0.9953826600638365</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4207910145135806</v>
+        <v>0.9953826373295354</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4207910978726849</v>
+        <v>0.9953827206886396</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4207911963879901</v>
+        <v>0.9953828192039449</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4207910296697814</v>
+        <v>0.9953826524857362</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4207910145135806</v>
+        <v>0.9953826373295354</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4207909842011791</v>
+        <v>0.9953826070171339</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4207909690449783</v>
+        <v>0.995382591860933</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4207910069354803</v>
+        <v>0.995382629751435</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4207910220916809</v>
+        <v>0.9953826449076356</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.970767248321669e-06</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4207910145135806</v>
+        <v>0.9953826373295354</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_1_000007.xlsx
+++ b/out/Attention-mamba2_repeat_1_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01330051384866238</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.02000000000000013</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.02044745162129402</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.2300000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.02209447696805</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.5232970714569092</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.1901832967996597</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.04794830456376076</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.003575674258172512</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.03035747818648815</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.008524958044290543</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0200282484292984</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.007167305797338486</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.02430526912212372</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.02123238705098629</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.01099769491702318</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.06120340898633003</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.01495196484029293</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.01964091323316097</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0003279416123405099</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.03685745596885681</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.01880608685314655</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.05607045441865921</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.2064894288778305</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.07407195866107941</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.02943542413413525</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.01530103012919426</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.009859184734523296</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0221982765942812</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.04610630869865417</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.03010648116469383</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0200259517878294</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.03666058927774429</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.01180494204163551</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.01377800572663546</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.01064833253622055</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.3174385726451874</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.5333669781684875</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.5009716153144836</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.3676735460758209</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-3.516261771006975e-05</v>
+        <v>-2.374188724905252e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.4053729746823554</v>
+        <v>0.2737088198054883</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.3402681350708008</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>0.8113727343818626</v>
+        <v>0.5478408956059538</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.06078750852185627</v>
+        <v>0.04104385848346254</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.3241178691387177</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.5270305589340839</v>
+        <v>0.3558523317891599</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.07600410788781901</v>
+        <v>0.05131817791221478</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.1243914067745209</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>0.6182610332445521</v>
+        <v>0.4174514153839927</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1089515282151813</v>
+        <v>0.07356452734066871</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.1838952749967575</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.760203086455992</v>
+        <v>0.5132911398550274</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.116556902154839</v>
+        <v>0.07869912454886685</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.1308561563491821</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.8843731604550048</v>
+        <v>0.5971310431035201</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1235268231524168</v>
+        <v>0.08340520947857311</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.09236634522676468</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.014878724464581</v>
+        <v>0.6852490732180814</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.05574469197845421</v>
+        <v>0.03763988566566401</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.1227251589298248</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.002739967705321</v>
+        <v>0.6770528489537041</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02692278149100792</v>
+        <v>0.01817834438752623</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0120195746421814</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.000795794483602</v>
+        <v>0.675740137249484</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01282679925930463</v>
+        <v>0.008659070097109081</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01345116645097733</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.9995063356691005</v>
+        <v>0.6748678667302993</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.00379661771500555</v>
+        <v>0.002562109210075422</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.005813665688037872</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6482190499120558</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.9942625675800382</v>
+        <v>0.6713256341973552</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002509625022824128</v>
+        <v>0.001692564140025768</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01636799424886703</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6482190499120558</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.9954838473327164</v>
+        <v>0.6721485431140889</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001282013293605033</v>
+        <v>0.0008638323686951406</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.02867560088634491</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9955367761012688</v>
+        <v>0.6721826568485764</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0006533570378990008</v>
+        <v>0.0004399446647574287</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.03664541617035866</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6502358700668159</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.9955607340108159</v>
+        <v>0.6721972124257304</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002425013679188365</v>
+        <v>0.00016227156669744</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.03267396986484528</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.850235870066816</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.9953916308557508</v>
+        <v>0.6720814738013171</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001303009802704108</v>
+        <v>8.575065749844627e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.03101173043251038</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.16</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.9954088362657181</v>
+        <v>0.6720914358767597</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>6.016785594578292e-05</v>
+        <v>3.871014728070806e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.006766699254512787</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.9953987854433987</v>
+        <v>0.6720830178176805</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.534215981483665e-05</v>
+        <v>2.255074328818113e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01606506854295731</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.9954092714339162</v>
+        <v>0.6720885936160828</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.558738314970903e-05</v>
+        <v>9.411168204796322e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.1024629026651382</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.6482190499120558</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.9954061105966873</v>
+        <v>0.6720848492020007</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.990931307851776e-06</v>
+        <v>1.993651915496244e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.06381700932979584</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.9954004618750396</v>
+        <v>0.6720794163155286</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.395731888813558e-06</v>
+        <v>-1.162560866711865e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.03814397379755974</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6482190499120559</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.9953985383989552</v>
+        <v>0.6720763743857638</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.503166167089948e-06</v>
+        <v>-2.668777444726632e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.04964885860681534</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.99539285212137</v>
+        <v>0.6720709168673735</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.009630925953388214</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6502358700668159</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.9953874416514523</v>
+        <v>0.6720656428032632</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.03994692862033844</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.9953826070171339</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.06009306013584137</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.9953824630332263</v>
+        <v>0.67206558217846</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.04036203026771545</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4482190499120557</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.995382440298925</v>
+        <v>0.6720655594441586</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.06507871299982071</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.9953827585791417</v>
+        <v>0.6720658777243753</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.02962570078670979</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.9953838498255986</v>
+        <v>0.6720669689708322</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.009639602154493332</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.9953831602184626</v>
+        <v>0.6720662793636962</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.00598684698343277</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.9953831905308643</v>
+        <v>0.6720663096760979</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.0346066951751709</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.6482190499120558</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.9953830010783542</v>
+        <v>0.6720661202235878</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.02201742678880692</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.9953830541250571</v>
+        <v>0.6720661732702907</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.005564317107200623</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.16</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.9953831071717599</v>
+        <v>0.6720662263169936</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01244605332612991</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.995383069281258</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.003355085849761963</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.9953829404535512</v>
+        <v>0.6720660595987848</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01145490258932114</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.9953827964696437</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.002540238201618195</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.9953826373295354</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.004254437983036041</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.4482190499120557</v>
+        <v>-0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.9953826903762382</v>
+        <v>0.6720658095214719</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.08535975962877274</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.9953826373295354</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.01591518521308899</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.6482190499120559</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.9953826373295354</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.02403033524751663</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.9953824554551258</v>
+        <v>0.6720655746003594</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.04043892025947571</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.9953826221733345</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.0008446722058579326</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.9953828192039449</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.08707871288061142</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.9953826600638365</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.005812384188175201</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.9953826979543385</v>
+        <v>0.6720658170995721</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.04208892956376076</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.850235870066816</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.9953828949849487</v>
+        <v>0.6720660141301823</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.01785974204540253</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.9953828722506475</v>
+        <v>0.6720659913958812</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.02335327118635178</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.4482190499120557</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.9953827206886396</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.02211841195821762</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.297446509901492</v>
+        <v>0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.9953826449076356</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0124543085694313</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6482190499120559</v>
+        <v>0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.9953827434229409</v>
+        <v>0.6720658625681745</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.04684582352638245</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.9953827510010411</v>
+        <v>0.6720658701462748</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.03323454409837723</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.9953830162345551</v>
+        <v>0.6720661353797887</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01032010465860367</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.9953827206886396</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02573812007904053</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.9953829631878524</v>
+        <v>0.6720660823330861</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.006116822361946106</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.9953830465469568</v>
+        <v>0.6720661656921904</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.04933807626366615</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.4482190499120557</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.9953828798287481</v>
+        <v>0.6720659989739817</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.02112337574362755</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.6482190499120558</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.995383069281258</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.03544066846370697</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.6482190499120558</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.9953827206886396</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.0716252475976944</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.6482190499120558</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.995382516079929</v>
+        <v>0.6720656352251626</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.08084195852279663</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.297446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.995382629751435</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.013570636510849</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.9953826449076356</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.01876487582921982</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.297446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.9953824099865235</v>
+        <v>0.6720655291317571</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.08189747482538223</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.297446509901492</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.9953824706113267</v>
+        <v>0.6720655897565603</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.07080736011266708</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.6482190499120558</v>
+        <v>-0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.99538234178362</v>
+        <v>0.6720654609288536</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.03286082297563553</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.4482190499120557</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.9953824781894269</v>
+        <v>0.6720655973346605</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.02771949768066406</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.4482190499120557</v>
+        <v>-0.16</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.9953826524857362</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.02437111735343933</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.9953827964696437</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01897035539150238</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.995382629751435</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.008661746978759766</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.9953826221733345</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.07563089579343796</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.9953823342055194</v>
+        <v>0.6720654533507531</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.06593190133571625</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.9953823493617202</v>
+        <v>0.6720654685069539</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.07551731169223785</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.9953825767047322</v>
+        <v>0.6720656958499658</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.03126693516969681</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.9953825615485313</v>
+        <v>0.6720656806937649</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.07483316957950592</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.9953826676419368</v>
+        <v>0.6720657867871704</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.0609717108309269</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.9953823948303225</v>
+        <v>0.6720655139755563</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.07243865728378296</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.097446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.9953824933456278</v>
+        <v>0.6720656124908615</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.07715805619955063</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.097446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.9953826449076356</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.07576858997344971</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.097446509901492</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.9953826600638365</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.0793079137802124</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.097446509901492</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.9953826373295354</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.02632953971624374</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.9953827206886396</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.07439439743757248</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.9953828192039449</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.06808909773826599</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.9953826524857362</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.07075952738523483</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.9953826373295354</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.07707930356264114</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.9953826070171339</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.07699543982744217</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.995382591860933</v>
+        <v>0.6720657110061666</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.07263863831758499</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.995382629751435</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.02554644644260406</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.7200000000000002</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.9953826449076356</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.0002672747941687703</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.097446509901492</v>
+        <v>-1</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.9953826373295354</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_1_000007.xlsx
+++ b/out/Attention-mamba2_repeat_1_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.01330051384866238</v>
+        <v>-0.01330257020890713</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.02000000000000013</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.02044745162129402</v>
+        <v>-0.0204499289393425</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.2300000000000001</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.02209447696805</v>
+        <v>0.02209264785051346</v>
       </c>
       <c r="JB4" t="n">
         <v>0.1600000000000001</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.5232970714569092</v>
+        <v>-0.5232997536659241</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.5799999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.1901832967996597</v>
+        <v>-0.1901861578226089</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.4399999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.04794830456376076</v>
+        <v>-0.04795092344284058</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.003575674258172512</v>
+        <v>-0.003525413107126951</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.4399999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.03035747818648815</v>
+        <v>-0.03035975061357021</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.3</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.008524958044290543</v>
+        <v>-0.008527018129825592</v>
       </c>
       <c r="JB10" t="n">
         <v>0.5799999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0200282484292984</v>
+        <v>-0.0200304202735424</v>
       </c>
       <c r="JB11" t="n">
         <v>0.4399999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.007167305797338486</v>
+        <v>-0.007169336546212435</v>
       </c>
       <c r="JB12" t="n">
         <v>0.5799999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.02430526912212372</v>
+        <v>-0.02425779029726982</v>
       </c>
       <c r="JB13" t="n">
         <v>0.4399999999999999</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.02123238705098629</v>
+        <v>-0.02123460359871387</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.01099769491702318</v>
+        <v>-0.01099984440952539</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.06120340898633003</v>
+        <v>-0.06120584160089493</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.01495196484029293</v>
+        <v>-0.01495411433279514</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.16</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.01964091323316097</v>
+        <v>-0.01964310929179192</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.16</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.0003279416123405099</v>
+        <v>-0.0003298700321465731</v>
       </c>
       <c r="JB19" t="n">
         <v>0.7199999999999999</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.03685745596885681</v>
+        <v>-0.03685974329710007</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.01880608685314655</v>
+        <v>-0.01880817487835884</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.05607045441865921</v>
+        <v>-0.05607285350561142</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.2064894288778305</v>
+        <v>-0.2064922899007797</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.07407195866107941</v>
+        <v>-0.07407457381486893</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.02943542413413525</v>
+        <v>-0.02943776734173298</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.16</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.01530103012919426</v>
+        <v>-0.01530323922634125</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.009859184734523296</v>
+        <v>-0.0098612941801548</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.0221982765942812</v>
+        <v>-0.02214646898210049</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.04610630869865417</v>
+        <v>-0.04610884189605713</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.03010648116469383</v>
+        <v>-0.03010895103216171</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.0200259517878294</v>
+        <v>-0.02002827636897564</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.03666058927774429</v>
+        <v>-0.03666143119335175</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.02000000000000007</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.01180494204163551</v>
+        <v>-0.01180684007704258</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.01377800572663546</v>
+        <v>-0.01378016266971827</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5799999999999998</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.01064833253622055</v>
+        <v>-0.01065053325146437</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.3174385726451874</v>
+        <v>-0.3174418210983276</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.5333669781684875</v>
+        <v>-0.5333690047264099</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.5009716153144836</v>
+        <v>-0.5009738802909851</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.3676735460758209</v>
+        <v>-0.3676717877388</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.3402681350708008</v>
+        <v>-0.3402666449546814</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.3241178691387177</v>
+        <v>-0.3241161704063416</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.1243914067745209</v>
+        <v>-0.1243896037340164</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.1838952749967575</v>
+        <v>-0.1838934272527695</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.7199999999999999</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.1308561563491821</v>
+        <v>-0.1308531314134598</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0.5971310431035201</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.09236634522676468</v>
+        <v>-0.09236272424459457</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC45" t="n">
         <v>0.6852490732180814</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.1227251589298248</v>
+        <v>-0.1227215453982353</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0.6770528489537041</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.0120195746421814</v>
+        <v>-0.012074314057827</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0.675740137249484</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.01345116645097733</v>
+        <v>-0.01344990357756615</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
         <v>0.6748678667302993</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.005813665688037872</v>
+        <v>0.005560207646340132</v>
       </c>
       <c r="JB49" t="n">
         <v>0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.01636799424886703</v>
+        <v>0.01636829227209091</v>
       </c>
       <c r="JB50" t="n">
         <v>0.8599999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.02867560088634491</v>
+        <v>-0.0286753922700882</v>
       </c>
       <c r="JB51" t="n">
         <v>0.7199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.03664541617035866</v>
+        <v>-0.03665302693843842</v>
       </c>
       <c r="JB52" t="n">
         <v>0.5799999999999998</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.03267396986484528</v>
+        <v>-0.03267467394471169</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.4399999999999999</v>
+        <v>-0.16</v>
       </c>
       <c r="JC53" t="n">
         <v>0.6720814738013171</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.03101173043251038</v>
+        <v>-0.03101126849651337</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.16</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.006766699254512787</v>
+        <v>-0.006766602862626314</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.02000000000000007</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.01606506854295731</v>
+        <v>-0.01606454700231552</v>
       </c>
       <c r="JB56" t="n">
         <v>0.1199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.1024629026651382</v>
+        <v>0.1024601459503174</v>
       </c>
       <c r="JB57" t="n">
         <v>0.8599999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.06381700932979584</v>
+        <v>0.06381672620773315</v>
       </c>
       <c r="JB58" t="n">
         <v>0.8599999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.03814397379755974</v>
+        <v>0.03814306855201721</v>
       </c>
       <c r="JB59" t="n">
         <v>0.8599999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.04964885860681534</v>
+        <v>-0.04964818805456161</v>
       </c>
       <c r="JB60" t="n">
         <v>0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.009630925953388214</v>
+        <v>-0.00963091105222702</v>
       </c>
       <c r="JB61" t="n">
         <v>0.5799999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.03994692862033844</v>
+        <v>-0.03994636237621307</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.02000000000000007</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.06009306013584137</v>
+        <v>-0.06009475886821747</v>
       </c>
       <c r="JB63" t="n">
         <v>0.1199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.04036203026771545</v>
+        <v>0.04031981900334358</v>
       </c>
       <c r="JB64" t="n">
         <v>0.1199999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.06507871299982071</v>
+        <v>0.06507723778486252</v>
       </c>
       <c r="JB65" t="n">
         <v>0.8599999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.02962570078670979</v>
+        <v>0.02962362021207809</v>
       </c>
       <c r="JB66" t="n">
         <v>0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.009639602154493332</v>
+        <v>0.009637489914894104</v>
       </c>
       <c r="JB67" t="n">
         <v>0.8599999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.00598684698343277</v>
+        <v>0.006045881193131208</v>
       </c>
       <c r="JB68" t="n">
         <v>0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.0346066951751709</v>
+        <v>0.03460324555635452</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.02000000000000007</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.02201742678880692</v>
+        <v>-0.02202090620994568</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.02000000000000007</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.005564317107200623</v>
+        <v>-0.005564265418797731</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.16</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.01244605332612991</v>
+        <v>0.01244499534368515</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.3</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.003355085849761963</v>
+        <v>-0.003354639280587435</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.3</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.01145490258932114</v>
+        <v>-0.01145449280738831</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.3</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.002540238201618195</v>
+        <v>-0.002540149260312319</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.3</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.004254437983036041</v>
+        <v>0.004254742991179228</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.16</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.08535975962877274</v>
+        <v>0.08535609394311905</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.16</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.01591518521308899</v>
+        <v>0.01591211557388306</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.3</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.02403033524751663</v>
+        <v>-0.02402979135513306</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.3</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.04043892025947571</v>
+        <v>-0.04043804854154587</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.3</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.0008446722058579326</v>
+        <v>-0.0008444491541013122</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.5799999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.08707871288061142</v>
+        <v>0.08707515895366669</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.005812384188175201</v>
+        <v>-0.005811959970742464</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.5799999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.04208892956376076</v>
+        <v>-0.04209648072719574</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.01785974204540253</v>
+        <v>-0.0178593322634697</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.02335327118635178</v>
+        <v>0.02335242182016373</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.02211841195821762</v>
+        <v>0.02211753278970718</v>
       </c>
       <c r="JB87" t="n">
         <v>0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.0124543085694313</v>
+        <v>0.01245560497045517</v>
       </c>
       <c r="JB88" t="n">
         <v>0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.04684582352638245</v>
+        <v>-0.04686296731233597</v>
       </c>
       <c r="JB89" t="n">
         <v>0.16</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.03323454409837723</v>
+        <v>-0.0332338809967041</v>
       </c>
       <c r="JB90" t="n">
         <v>0.02000000000000007</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.01032010465860367</v>
+        <v>0.01031570881605148</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.8599999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.02573812007904053</v>
+        <v>-0.02573736011981964</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.006116822361946106</v>
+        <v>-0.006117195356637239</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.3</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.04933807626366615</v>
+        <v>0.04933363571763039</v>
       </c>
       <c r="JB94" t="n">
         <v>0.1600000000000001</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.02112337574362755</v>
+        <v>0.02106563746929169</v>
       </c>
       <c r="JB95" t="n">
         <v>0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.03544066846370697</v>
+        <v>-0.03544013947248459</v>
       </c>
       <c r="JB96" t="n">
         <v>0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.0716252475976944</v>
+        <v>0.07125195860862732</v>
       </c>
       <c r="JB97" t="n">
         <v>0.5799999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.08084195852279663</v>
+        <v>0.08083878457546234</v>
       </c>
       <c r="JB98" t="n">
         <v>0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.013570636510849</v>
+        <v>0.01357072591781616</v>
       </c>
       <c r="JB99" t="n">
         <v>0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.01876487582921982</v>
+        <v>0.01876338571310043</v>
       </c>
       <c r="JB100" t="n">
         <v>0.5799999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.08189747482538223</v>
+        <v>0.08189418911933899</v>
       </c>
       <c r="JB101" t="n">
         <v>0.3</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.07080736011266708</v>
+        <v>0.0708039402961731</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.03286082297563553</v>
+        <v>-0.03286295011639595</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.02000000000000007</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.02771949768066406</v>
+        <v>0.02771869301795959</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.16</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.02437111735343933</v>
+        <v>0.02437012642621994</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.16</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.01897035539150238</v>
+        <v>0.01896974444389343</v>
       </c>
       <c r="JB106" t="n">
         <v>0.7199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.008661746978759766</v>
+        <v>0.008661843836307526</v>
       </c>
       <c r="JB107" t="n">
         <v>0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.07563089579343796</v>
+        <v>0.07562698423862457</v>
       </c>
       <c r="JB108" t="n">
         <v>0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.06593190133571625</v>
+        <v>0.06592883169651031</v>
       </c>
       <c r="JB109" t="n">
         <v>0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.07551731169223785</v>
+        <v>0.07551433891057968</v>
       </c>
       <c r="JB110" t="n">
         <v>0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.03126693516969681</v>
+        <v>0.03126605600118637</v>
       </c>
       <c r="JB111" t="n">
         <v>0.8599999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.07483316957950592</v>
+        <v>0.07483005523681641</v>
       </c>
       <c r="JB112" t="n">
         <v>0.8599999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.0609717108309269</v>
+        <v>0.06096859276294708</v>
       </c>
       <c r="JB113" t="n">
         <v>0.8599999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.07243865728378296</v>
+        <v>0.07243571430444717</v>
       </c>
       <c r="JB114" t="n">
         <v>0.8599999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.07715805619955063</v>
+        <v>0.07715532183647156</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.07576858997344971</v>
+        <v>0.07576575130224228</v>
       </c>
       <c r="JB116" t="n">
         <v>0.1199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.0793079137802124</v>
+        <v>0.07929036766290665</v>
       </c>
       <c r="JB117" t="n">
         <v>0.1199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.02632953971624374</v>
+        <v>0.02632886916399002</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.02000000000000007</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.07439439743757248</v>
+        <v>0.07439113408327103</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.16</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.06808909773826599</v>
+        <v>0.06808622181415558</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.3</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.07075952738523483</v>
+        <v>0.0707567110657692</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.02000000000000007</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.07707930356264114</v>
+        <v>0.07707660645246506</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.16</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.07699543982744217</v>
+        <v>0.07699266076087952</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.07263863831758499</v>
+        <v>0.07263559103012085</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.02554644644260406</v>
+        <v>0.02554650604724884</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.7200000000000002</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.0002672747941687703</v>
+        <v>0.0002675201976671815</v>
       </c>
       <c r="JB126" t="n">
         <v>-1</v>
